--- a/简易测式/v3.0/对比表格.xlsx
+++ b/简易测式/v3.0/对比表格.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>输入</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>初始情况都是相同的，有对话记录</t>
+  </si>
+  <si>
+    <t>标准模式这回发力了</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1013,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.3451327433628" customWidth="1"/>
@@ -1071,12 +1074,18 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="2">
+        <v>712000</v>
+      </c>
+      <c r="C4" s="2">
+        <v>12500</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.94</v>
+      </c>
       <c r="E4" s="3">
         <f>(B4*(D4*0.05+(1-D4)*1.5)+C4*4.5)/1000000</f>
-        <v>0</v>
+        <v>0.153794</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1097,6 +1106,11 @@
     <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
